--- a/report-2026-06-08.xlsx
+++ b/report-2026-06-08.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-08T23:42:18+05:30</t>
+    <t>Generated 2026-06-08T23:58:03+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-08T23:40:10+05:30 (2m8s ago)</t>
+    <t>2026-06-08T23:55:37+05:30 (2m25s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -204,10 +204,43 @@
     <t>stale-takeover</t>
   </si>
   <si>
+    <t>2026-06-08T23:45:21.045245+05:30</t>
+  </si>
+  <si>
+    <t>23:45:21.045</t>
+  </si>
+  <si>
+    <t>renewed</t>
+  </si>
+  <si>
+    <t>2026-06-08T23:50:20.3164757+05:30</t>
+  </si>
+  <si>
+    <t>23:50:20.316</t>
+  </si>
+  <si>
+    <t>2026-06-08T23:51:53.3444626+05:30</t>
+  </si>
+  <si>
+    <t>23:51:53.344</t>
+  </si>
+  <si>
+    <t>2026-06-08T23:53:00.5826369+05:30</t>
+  </si>
+  <si>
+    <t>23:53:00.582</t>
+  </si>
+  <si>
+    <t>2026-06-08T23:55:37.4511138+05:30</t>
+  </si>
+  <si>
+    <t>23:55:37.451</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-08T23:42:18+05:30</t>
+    <t>2026-06-08T23:58:03+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -762,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.58</t>
+          <t>10.0.59</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -802,12 +835,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 23s</t>
+          <t>0h 2m 41s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:39:54</t>
+          <t>2026-06-08 23:55:21</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -817,12 +850,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:39:54</t>
+          <t>2026-06-08 23:55:21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 1m 36s</t>
+          <t>0h 3m 26s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -832,7 +865,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:42:18</t>
+          <t>23:58:03</t>
         </is>
       </c>
     </row>
@@ -869,7 +902,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.58</t>
+          <t>10.0.59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -889,17 +922,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>109146.2</t>
+          <t>94066.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -909,7 +942,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -924,12 +957,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:39:54</t>
+          <t>2026-06-08 23:55:21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 1m 36s</t>
+          <t>0h 3m 11s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -939,7 +972,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:42:18</t>
+          <t>23:58:03</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1086,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[stale-takeover]</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-08T23:40:10.5495809+05:30</t>
+          <t>2026-06-08T23:55:37.4511138+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1068,12 +1101,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:40:10.549</t>
+          <t>23:55:37.451</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stale-takeover</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1101,7 +1134,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>stale-takeover</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1267,6 +1300,321 @@
       <c r="G3" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1780943233682</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23:57:13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kRx060GX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1780943233790</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23:57:13</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>kRx060GX</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1780943234407</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23:57:14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apzw9sxr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1780943234507</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23:57:14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>apzw9sxr</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1780943235211</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23:57:15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>62OYvYNz</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1780943235306</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23:57:15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>62OYvYNz</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1780943241868</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23:57:21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>assist_closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>kRx060GX</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1780943242590</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>23:57:22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>assist_closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apzw9sxr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1780943244346</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23:57:24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>assist_closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>62OYvYNz</t>
         </is>
       </c>
     </row>
@@ -1796,18 +2144,208 @@
         <v>44</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4">
+        <v>10</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="A28" s="4">
+        <v>11</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E28">
+      <c r="F28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>9</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4">
+        <v>12</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4">
+        <v>13</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4">
+        <v>14</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
